--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260825.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260825.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>131,735</t>
+          <t>132,235</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>26.64%</t>
+          <t>26.40%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>7.99%</t>
+          <t>7.80%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>95,630</t>
+          <t>95,930</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.69%</t>
+          <t>7.78%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>48,665</t>
+          <t>48,765</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>6.29%</t>
+          <t>6.57%</t>
         </is>
       </c>
     </row>
@@ -699,100 +699,100 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>116,145</t>
+          <t>116,395</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.51%</t>
+          <t>5.49%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>NOW US</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>ServiceNow Inc</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>245,441,045</t>
+          <t>57,140</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.34%</t>
+          <t>4.06%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>NOW US</t>
+          <t>EQIX US</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>ServiceNow Inc</t>
+          <t>Equinix公司</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>57,140</t>
+          <t>5,435</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.13%</t>
+          <t>3.27%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>EQIX US</t>
+          <t>SO US</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Equinix公司</t>
+          <t>南方公司</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>5,435</t>
+          <t>62,885</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.24%</t>
+          <t>3.17%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>SO US</t>
+          <t>CEG US</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>南方公司</t>
+          <t>星座能源公司</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>62,735</t>
+          <t>19,015</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.19%</t>
+          <t>2.97%</t>
         </is>
       </c>
     </row>
@@ -809,78 +809,78 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>43,265</t>
+          <t>43,365</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.98%</t>
+          <t>2.95%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>CEG US</t>
+          <t>NET US</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>星座能源公司</t>
+          <t>Cloudflare公司</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>18,915</t>
+          <t>17,613</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.92%</t>
+          <t>2.74%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>NET US</t>
+          <t>HPE US</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Cloudflare公司</t>
+          <t>慧與</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>17,513</t>
+          <t>73,795</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.77%</t>
+          <t>2.21%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>HPE US</t>
+          <t>DLR US</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>慧與</t>
+          <t>數位不動產信託公司</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>73,645</t>
+          <t>19,465</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.18%</t>
+          <t>2.10%</t>
         </is>
       </c>
     </row>
@@ -897,232 +897,232 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>30,180</t>
+          <t>30,330</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>2.09%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>DLR US</t>
+          <t>D US</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>數位不動產信託公司</t>
+          <t>道明尼能源公司</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>19,465</t>
+          <t>49,045</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>1.84%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>D US</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>道明尼能源公司</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>48,945</t>
+          <t>25,498</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>1.52%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>XEL US</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>Xcel 能源</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>25,398</t>
+          <t>34,770</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.50%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>XEL US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Xcel 能源</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>34,670</t>
+          <t>18,720</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.46%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>EXC US</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>愛克斯龍公司</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>18,620</t>
+          <t>56,898</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.41%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>EXC US</t>
+          <t>NBIS US</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>愛克斯龍公司</t>
+          <t>尼比厄斯集團公眾有限公司</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>56,898</t>
+          <t>11,251</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.40%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>NBIS US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>尼比厄斯集團公眾有限公司</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>11,151</t>
+          <t>121,715</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.33%</t>
+          <t>1.25%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>ED US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>聯合愛迪生</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>121,715</t>
+          <t>20,438</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.23%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>ED US</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>聯合愛迪生</t>
+          <t>Astera實驗室公司</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>20,438</t>
+          <t>7,690</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.22%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Astera實驗室公司</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>7,590</t>
+          <t>69,368,405</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.22%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>1.17%</t>
         </is>
       </c>
     </row>
@@ -1166,46 +1166,46 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.05%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>CRWV US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>15,171</t>
+          <t>18,767</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.93%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>CRWV US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>18,767</t>
+          <t>15,271</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.81%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.78%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>0.72%</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>691,840</t>
+          <t>486,007</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.27%</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>-205,833</t>
+          <t>125,249</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
